--- a/Assessment Questions/CDE/PYTHON FOUNDATION/Python Data Structures/Dictionary_ Object and methods/Dictionary.xlsx
+++ b/Assessment Questions/CDE/PYTHON FOUNDATION/Python Data Structures/Dictionary_ Object and methods/Dictionary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,11 +454,6 @@
           <t>A) key-value B) list C) set D) tuple</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -476,11 +471,6 @@
           <t>A) immutable B) mutable C) both D) none</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,11 +488,6 @@
           <t>A) any type B) only int C) only str D) none</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -522,7 +507,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -542,11 +527,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -566,7 +546,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -586,11 +566,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -608,11 +583,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -630,11 +600,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -654,7 +619,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -676,7 +641,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -696,11 +661,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -718,11 +678,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -740,11 +695,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -762,11 +712,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -784,11 +729,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -808,7 +748,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -828,11 +768,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -852,7 +787,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -870,11 +805,6 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Hard</t>
         </is>
       </c>
     </row>
